--- a/data/trans_bre/IP25-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP25-Clase-trans_bre.xlsx
@@ -504,7 +504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:H18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -515,8 +515,6 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -533,15 +531,13 @@
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
-      <c r="F1" s="3" t="n"/>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>Brecha de género relativa</t>
         </is>
       </c>
+      <c r="G1" s="3" t="n"/>
       <c r="H1" s="3" t="n"/>
-      <c r="I1" s="3" t="n"/>
-      <c r="J1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
@@ -563,27 +559,17 @@
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>2007</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>2012</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
           <t>2016</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>2023</t>
         </is>
       </c>
     </row>
@@ -596,8 +582,6 @@
       <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="n"/>
       <c r="H3" s="2" t="n"/>
-      <c r="I3" s="2" t="n"/>
-      <c r="J3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -627,27 +611,17 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>-0,83%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-0,83%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
           <t>-1,44%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
     </row>
@@ -660,42 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,76; 9,96</t>
+          <t>-5,09; 10,44</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,87; 7,02</t>
+          <t>-8,18; 6,89</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-10,72; 6,63</t>
+          <t>-9,77; 7,74</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-5,81; 13,09</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-6,49; 12,31</t>
+          <t>-8,79; 8,04</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-8,44; 8,25</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-11,74; 7,91</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>-10,97; 9,32</t>
         </is>
       </c>
     </row>
@@ -727,27 +691,17 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>-0,5%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-0,5%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
           <t>-2,26%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
     </row>
@@ -760,42 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,33; 14,79</t>
+          <t>-1,68; 14,95</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-7,24; 7,63</t>
+          <t>-7,88; 6,6</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-8,46; 4,18</t>
+          <t>-8,47; 4,2</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-1,94; 19,34</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-2,6; 19,44</t>
+          <t>-8,43; 7,91</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-7,81; 8,92</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-8,94; 4,73</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>-9,13; 4,71</t>
         </is>
       </c>
     </row>
@@ -827,27 +771,17 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>-1,62%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>-1,62%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
           <t>2,43%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
     </row>
@@ -860,42 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-9,15; 5,72</t>
+          <t>-9,58; 5,68</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,93; 6,99</t>
+          <t>-7,21; 7,34</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,71; 10,11</t>
+          <t>-5,81; 9,79</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-10,18; 6,35</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-9,75; 6,48</t>
+          <t>-7,73; 8,48</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-7,4; 8,07</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-6,05; 11,93</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>-6,06; 11,52</t>
         </is>
       </c>
     </row>
@@ -927,27 +851,17 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>-6,52%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-6,52%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
           <t>-2,32%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
     </row>
@@ -960,42 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 8,16</t>
+          <t>-2,1; 7,93</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-11,29; -1,25</t>
+          <t>-10,68; -1,25</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-6,43; 1,99</t>
+          <t>-6,12; 2,13</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-2,28; 9,35</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 9,64</t>
+          <t>-11,5; -1,53</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-11,95; -1,45</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-6,75; 2,24</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>-6,47; 2,35</t>
         </is>
       </c>
     </row>
@@ -1027,27 +931,17 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>-2,35%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-2,35%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
           <t>0,96%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 12,2</t>
+          <t>-0,98; 11,82</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-7,67; 4,31</t>
+          <t>-7,72; 4,12</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,77; 6,52</t>
+          <t>-4,88; 6,12</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-1,06; 14,16</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 14,91</t>
+          <t>-8,27; 4,83</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-8,29; 4,87</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-5,06; 7,53</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>-5,23; 6,99</t>
         </is>
       </c>
     </row>
@@ -1127,27 +1011,17 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
           <t>-7,17%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1034,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-6,75; 9,27</t>
+          <t>-5,88; 9,03</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-8,87; 8,86</t>
+          <t>-8,03; 8,48</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-14,05; 0,97</t>
+          <t>-14,31; 0,01</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-6,21; 10,34</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-7,02; 10,96</t>
+          <t>-8,69; 9,93</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-9,75; 10,38</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>-14,64; 1,02</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>-14,66; 0,01</t>
         </is>
       </c>
     </row>
@@ -1227,27 +1091,17 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>-2,67%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-2,67%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
           <t>-1,44%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1114,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,12; 5,4</t>
+          <t>-0,0; 5,34</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-5,13; 0,44</t>
+          <t>-5,11; 0,29</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,8; 1,15</t>
+          <t>-3,62; 1,39</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-0,01; 6,21</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,14; 6,32</t>
+          <t>-5,54; 0,31</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-5,58; 0,49</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>-4,16; 1,27</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
+          <t>-3,94; 1,54</t>
         </is>
       </c>
     </row>
@@ -1308,13 +1152,13 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="C1:E1"/>
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="A12:A13"/>
     <mergeCell ref="A4:A5"/>
+    <mergeCell ref="F1:H1"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="C1:F1"/>
     <mergeCell ref="A16:A17"/>
-    <mergeCell ref="G1:J1"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="A10:A11"/>
     <mergeCell ref="A14:A15"/>

--- a/data/trans_bre/IP25-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP25-Clase-trans_bre.xlsx
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,09; 10,44</t>
+          <t>-5,23; 10,17</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-8,18; 6,89</t>
+          <t>-7,41; 6,41</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-9,77; 7,74</t>
+          <t>-8,98; 6,89</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,81; 13,09</t>
+          <t>-5,93; 12,64</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-8,79; 8,04</t>
+          <t>-7,91; 7,55</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-10,97; 9,32</t>
+          <t>-10,03; 8,11</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,68; 14,95</t>
+          <t>-2,25; 14,38</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-7,88; 6,6</t>
+          <t>-7,46; 6,96</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-8,47; 4,2</t>
+          <t>-9,18; 3,91</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 19,34</t>
+          <t>-2,56; 18,76</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-8,43; 7,91</t>
+          <t>-7,92; 8,15</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-9,13; 4,71</t>
+          <t>-9,9; 4,4</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-9,58; 5,68</t>
+          <t>-9,1; 5,71</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,21; 7,34</t>
+          <t>-7,21; 8,22</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,81; 9,79</t>
+          <t>-4,71; 10,61</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-10,18; 6,35</t>
+          <t>-9,78; 6,43</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-7,73; 8,48</t>
+          <t>-7,62; 9,67</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-6,06; 11,52</t>
+          <t>-5,02; 12,63</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 7,93</t>
+          <t>-2,85; 7,39</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-10,68; -1,25</t>
+          <t>-10,98; -0,9</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-6,12; 2,13</t>
+          <t>-6,07; 2,29</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2,28; 9,35</t>
+          <t>-3,07; 8,59</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-11,5; -1,53</t>
+          <t>-11,75; -1,09</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-6,47; 2,35</t>
+          <t>-6,41; 2,52</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 11,82</t>
+          <t>-0,44; 11,7</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-7,72; 4,12</t>
+          <t>-8,48; 4,01</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,88; 6,12</t>
+          <t>-4,69; 6,42</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 14,16</t>
+          <t>-0,37; 14,05</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-8,27; 4,83</t>
+          <t>-9,2; 4,71</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-5,23; 6,99</t>
+          <t>-5,07; 7,38</t>
         </is>
       </c>
     </row>
@@ -1034,32 +1034,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-5,88; 9,03</t>
+          <t>-5,9; 8,9</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-8,03; 8,48</t>
+          <t>-8,7; 8,4</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-14,31; 0,01</t>
+          <t>-13,99; 0,47</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-6,21; 10,34</t>
+          <t>-6,25; 10,71</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-8,69; 9,93</t>
+          <t>-9,37; 9,65</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-14,66; 0,01</t>
+          <t>-14,69; 0,36</t>
         </is>
       </c>
     </row>
@@ -1114,32 +1114,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,0; 5,34</t>
+          <t>0,02; 5,59</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-5,11; 0,29</t>
+          <t>-4,98; 0,26</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,62; 1,39</t>
+          <t>-3,75; 1,4</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,01; 6,21</t>
+          <t>0,04; 6,6</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-5,54; 0,31</t>
+          <t>-5,38; 0,29</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-3,94; 1,54</t>
+          <t>-4,04; 1,56</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP25-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP25-Clase-trans_bre.xlsx
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,23; 10,17</t>
+          <t>-5,76; 9,96</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,41; 6,41</t>
+          <t>-7,87; 7,02</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-8,98; 6,89</t>
+          <t>-10,72; 6,63</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,93; 12,64</t>
+          <t>-6,49; 12,31</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-7,91; 7,55</t>
+          <t>-8,44; 8,25</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-10,03; 8,11</t>
+          <t>-11,74; 7,91</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-2,25; 14,38</t>
+          <t>-2,33; 14,79</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-7,46; 6,96</t>
+          <t>-7,24; 7,63</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-9,18; 3,91</t>
+          <t>-8,46; 4,18</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-2,56; 18,76</t>
+          <t>-2,6; 19,44</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-7,92; 8,15</t>
+          <t>-7,81; 8,92</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-9,9; 4,4</t>
+          <t>-8,94; 4,73</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-9,1; 5,71</t>
+          <t>-9,15; 5,72</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,21; 8,22</t>
+          <t>-6,93; 6,99</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,71; 10,61</t>
+          <t>-5,71; 10,11</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-9,78; 6,43</t>
+          <t>-9,75; 6,48</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-7,62; 9,67</t>
+          <t>-7,4; 8,07</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-5,02; 12,63</t>
+          <t>-6,05; 11,93</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,85; 7,39</t>
+          <t>-1,62; 8,16</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-10,98; -0,9</t>
+          <t>-11,29; -1,25</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-6,07; 2,29</t>
+          <t>-6,43; 1,99</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,07; 8,59</t>
+          <t>-1,78; 9,64</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-11,75; -1,09</t>
+          <t>-11,95; -1,45</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-6,41; 2,52</t>
+          <t>-6,75; 2,24</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 11,7</t>
+          <t>-0,46; 12,2</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-8,48; 4,01</t>
+          <t>-7,67; 4,31</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,69; 6,42</t>
+          <t>-4,77; 6,52</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 14,05</t>
+          <t>-0,41; 14,91</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-9,2; 4,71</t>
+          <t>-8,29; 4,87</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-5,07; 7,38</t>
+          <t>-5,06; 7,53</t>
         </is>
       </c>
     </row>
@@ -1034,32 +1034,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-5,9; 8,9</t>
+          <t>-6,75; 9,27</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-8,7; 8,4</t>
+          <t>-8,87; 8,86</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-13,99; 0,47</t>
+          <t>-14,05; 0,97</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-6,25; 10,71</t>
+          <t>-7,02; 10,96</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-9,37; 9,65</t>
+          <t>-9,75; 10,38</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-14,69; 0,36</t>
+          <t>-14,64; 1,02</t>
         </is>
       </c>
     </row>
@@ -1114,32 +1114,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,02; 5,59</t>
+          <t>0,12; 5,4</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-4,98; 0,26</t>
+          <t>-5,13; 0,44</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,75; 1,4</t>
+          <t>-3,8; 1,15</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,04; 6,6</t>
+          <t>0,14; 6,32</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-5,38; 0,29</t>
+          <t>-5,58; 0,49</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-4,04; 1,56</t>
+          <t>-4,16; 1,27</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP25-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP25-Clase-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -594,239 +603,163 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>2,19</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-0,74</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-1,25</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2,58%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-0,83%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-1,44%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>2.194104587873436</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-0.7444547686015879</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-1.245769070067881</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>0.02577351487835799</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>-0.008269761787407449</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>-0.0143739457305507</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-5,76; 9,96</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-7,87; 7,02</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-10,72; 6,63</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-6,49; 12,31</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-8,44; 8,25</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-11,74; 7,91</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-5.75596416200175</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-7.867854964986737</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-10.72066160994559</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>-0.06485924115188269</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-0.08435203442029215</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>-0.1174497774041517</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>9.960981949379063</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>7.021728724010738</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>6.625395567728306</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>0.1230891346123336</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>0.08247328541539851</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>0.07910490064180227</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Grupo III</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>6,18</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-0,45</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-2,06</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>7,49%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-0,5%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-2,26%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-2,33; 14,79</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-7,24; 7,63</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-8,46; 4,18</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-2,6; 19,44</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-7,81; 8,92</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-8,94; 4,73</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>6.177962341241871</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>-0.4464832513250694</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>-2.063544138337992</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>0.07493372009802224</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-0.004972098578705227</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.02259329197138708</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Grupo IV y V</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>-1,48</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>0,31</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>2,19</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-1,62%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0,35%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>2,43%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-2.328584503872238</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-7.236938066712899</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-8.461086159374458</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>-0.02596548207154133</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.07809026796852497</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.08942371501553623</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-9,15; 5,72</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-6,93; 6,99</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-5,71; 10,11</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-9,75; 6,48</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-7,4; 8,07</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-6,05; 11,93</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>14.78927256672904</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>7.627496005680028</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>4.175482956069259</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>0.1944106328642357</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.08920570615893783</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0.04726102449110959</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Grupo VI</t>
+          <t>Grupo IV y V</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -834,239 +767,163 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>2,78</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-6,06</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-2,15</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>3,15%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-6,52%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-2,32%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>-1.484331238372105</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.3146349333508658</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>2.189529123520939</v>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>-0.01621940587381841</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>0.003485725484092306</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>0.02432275294113921</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-1,62; 8,16</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-11,29; -1,25</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-6,43; 1,99</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-1,78; 9,64</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-11,95; -1,45</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-6,75; 2,24</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-9.149185385751867</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-6.930843073976719</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-5.708440615965811</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>-0.09753544652056766</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.07401489157863914</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-0.06052380389136958</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Grupo VII</t>
-        </is>
-      </c>
+      <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>5.719157574372403</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>6.985578274040213</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>10.11104359645982</v>
+      </c>
+      <c r="F12" s="6" t="n">
+        <v>0.06479453240625072</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>0.08074974994795441</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>0.1193368457577951</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>5,74</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>-2,13</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0,86</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>6,57%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-2,35%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0,96%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-0,46; 12,2</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-7,67; 4,31</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-4,77; 6,52</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-0,41; 14,91</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-8,29; 4,87</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-5,06; 7,53</t>
-        </is>
+      <c r="C13" s="5" t="n">
+        <v>2.783977220330824</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-6.059573248524797</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>-2.153195749158165</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>0.03154535084998181</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.06523700662925888</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.02321055183428001</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>No ha trabajado</t>
-        </is>
-      </c>
+      <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>1,56</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>0,32</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-6,87</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>1,72%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>0,36%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>-7,17%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-1.622900762103914</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-11.29310103530482</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-6.434309070012557</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>-0.01784202333216624</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.1194642259254153</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.06745528078267042</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>-6,75; 9,27</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>-8,87; 8,86</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>-14,05; 0,97</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>-7,02; 10,96</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>-9,75; 10,38</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>-14,64; 1,02</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>8.164413274546421</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>-1.2525580953854</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>1.987001016249256</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>0.09638691838682732</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>-0.01445306544425662</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.02242582980171307</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Grupo VII</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1074,77 +931,243 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>2,83</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>-2,43</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-1,32</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>3,23%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-2,67%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>-1,44%</t>
-        </is>
+      <c r="C16" s="5" t="n">
+        <v>5.744074758804219</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-2.127692569436734</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.8640023996486113</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>0.06569819889816304</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>-0.02353955197389365</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>0.009557888333677256</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>0,12; 5,4</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>-5,13; 0,44</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>-3,8; 1,15</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>0,14; 6,32</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>-5,58; 0,49</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>-4,16; 1,27</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-0.4588321371219696</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-7.673510987804091</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-4.769992638967303</v>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>-0.004099171360554426</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-0.082923914762506</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-0.05063324245348791</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>12.19853439287873</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>4.307621839289702</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>6.520428280554053</v>
+      </c>
+      <c r="F18" s="6" t="n">
+        <v>0.1491117586888637</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>0.04873871187117212</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>0.07531369285289928</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>1.556798866052655</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>0.3222033045356176</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>-6.874780265640512</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>0.01720265568849808</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>0.003587744116452242</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>-0.07174910602286062</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>-6.75491547031881</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>-8.867287763318428</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>-14.05330196147424</v>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>-0.0701819864112216</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>-0.09749494502465413</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>-0.1464347925498549</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>9.269907496094433</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>8.856931686799214</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>0.9739713716524764</v>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>0.1096341697187642</v>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>0.1037978519184227</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>0.01020065107106818</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>2.829430175312653</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>-2.429264457941926</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>-1.317382704051262</v>
+      </c>
+      <c r="F22" s="6" t="n">
+        <v>0.03228586735762806</v>
+      </c>
+      <c r="G22" s="6" t="n">
+        <v>-0.02670056183770205</v>
+      </c>
+      <c r="H22" s="6" t="n">
+        <v>-0.01444437644181193</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>0.1192039592084413</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>-5.126980675307276</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>-3.798083076593672</v>
+      </c>
+      <c r="F23" s="6" t="n">
+        <v>0.001359343770788085</v>
+      </c>
+      <c r="G23" s="6" t="n">
+        <v>-0.05575741818321787</v>
+      </c>
+      <c r="H23" s="6" t="n">
+        <v>-0.04155271057457931</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>5.40307106495362</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>0.4425093467725913</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>1.146381546005301</v>
+      </c>
+      <c r="F24" s="6" t="n">
+        <v>0.06321016031447767</v>
+      </c>
+      <c r="G24" s="6" t="n">
+        <v>0.004861008111696042</v>
+      </c>
+      <c r="H24" s="6" t="n">
+        <v>0.0126910896569283</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1153,15 +1176,15 @@
   </sheetData>
   <mergeCells count="10">
     <mergeCell ref="C1:E1"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="F1:H1"/>
+    <mergeCell ref="A19:A21"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
